--- a/NuclearCraft_FissionReactor_SourceData.xlsx
+++ b/NuclearCraft_FissionReactor_SourceData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="1" r:id="R71fe7e00aae142af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减速剂" sheetId="2" r:id="Rf258c718a7d5439d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反射器" sheetId="3" r:id="R122340d19bda4b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中子源" sheetId="4" r:id="Raa722c8900164951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中子防护屏" sheetId="5" r:id="Re4daa4af1fd14dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="辐照器配方" sheetId="6" r:id="R0452ff016a014268"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="散热器" sheetId="7" r:id="Ra237bfeafb334215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固体裂变燃料" sheetId="8" r:id="Ra7b06ae0ad244c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置映射" sheetId="9" r:id="R66a5c5d40bcb45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="1" r:id="R41bdb80f6ba74c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减速剂" sheetId="2" r:id="R9e682025a70f4b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反射器" sheetId="3" r:id="R33729e9bb3c34a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中子源" sheetId="4" r:id="R72fa9514276f4407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中子防护屏" sheetId="5" r:id="R6d7fb0194c0843f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="辐照器配方" sheetId="6" r:id="R94946b877ef64329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="散热器" sheetId="7" r:id="Re4bc5d186da249cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固体裂变燃料" sheetId="8" r:id="R4229a902fe644cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置映射" sheetId="9" r:id="Rdf41b0142a3d4def"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -218,7 +218,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SourceSummaryTable" displayName="SourceSummaryTable" ref="A3:B36" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SourceSummaryTable" displayName="SourceSummaryTable" ref="A3:B38" headerRowCount="1">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="项目"/>
     <x:tableColumn id="2" name="内容"/>
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ModeratorsTable" displayName="ModeratorsTable" ref="A3:H6" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ModeratorsTable" displayName="ModeratorsTable" ref="A3:H9" headerRowCount="1">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="类别"/>
     <x:tableColumn id="2" name="注册名/矿辞"/>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReflectorsTable" displayName="ReflectorsTable" ref="A3:I5" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReflectorsTable" displayName="ReflectorsTable" ref="A3:I7" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="类别"/>
     <x:tableColumn id="2" name="Meta ID"/>
@@ -594,10 +594,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="24" t="str">
-        <x:v>燃料数值来自 GreedyCraft nuclearcraft.cfg；有效值列按 BasicRecipe 的 fission_fuel_*_multiplier 默认倍率计算。</x:v>
+        <x:v>燃料、基础减速剂、基础反射器和中子源数值来自 GreedyCraft nuclearcraft.cfg；MoarReactorComponents 附加减速剂/反射器来自 CraftTweaker 脚本。</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>燃料数值来自 GreedyCraft nuclearcraft.cfg；有效值列按 BasicRecipe 的 fission_fuel_*_multiplier 默认倍率计算。</x:v>
+        <x:v>燃料、基础减速剂、基础反射器和中子源数值来自 GreedyCraft nuclearcraft.cfg；MoarReactorComponents 附加减速剂/反射器来自 CraftTweaker 脚本。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -613,7 +613,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B4" s="26" t="n">
-        <x:v>46191.5941787037</x:v>
+        <x:v>46193.22601953704</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -629,7 +629,7 @@
         <x:v>源码范围</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>基础 NuclearCraft 数据来自本仓库 NuclearCraft/src/main 下 Java 源码与本地化文件；燃料数值优先使用 GreedyCraft nuclearcraft.cfg；动态散热器来自 GreedyCraft CraftTweaker 注册脚本，并由 NuclearCraft CTRegistration/FissionPlacement 运行时注册。</x:v>
+        <x:v>基础 NuclearCraft 数据来自本仓库 NuclearCraft/src/main 下 Java 源码与本地化文件；燃料、基础减速剂、基础反射器和中子源数值优先使用 GreedyCraft nuclearcraft.cfg；MoarReactorComponents 附加减速剂/反射器与动态散热器来自 GreedyCraft CraftTweaker 注册脚本。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -848,25 +848,41 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="26" t="str">
-        <x:v>source.dynamicSinkRegistrationGlobal</x:v>
+        <x:v>source.moarReactorComponentsRecipes</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/global/nuclearcraft_registration.zs</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="26" t="str">
-        <x:v>source.dynamicSinkRegistrationMoarCofh</x:v>
+        <x:v>source.moarReactorComponentsGeneration</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarHeatSinks/mhsCOFH_gen.zs</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="26" t="str">
+        <x:v>source.dynamicSinkRegistrationGlobal</x:v>
+      </x:c>
+      <x:c r="B36" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/global/nuclearcraft_registration.zs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="26" t="str">
+        <x:v>source.dynamicSinkRegistrationMoarCofh</x:v>
+      </x:c>
+      <x:c r="B37" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarHeatSinks/mhsCOFH_gen.zs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="26" t="str">
         <x:v>source.dynamicSinkRegistrationMoarNcPlus</x:v>
       </x:c>
-      <x:c r="B36" s="26" t="str">
+      <x:c r="B38" s="26" t="str">
         <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarHeatSinks/mhsNCplus_gen.zs</x:v>
       </x:c>
     </x:row>
@@ -877,7 +893,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7623549da83f448e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R894bfff75544413b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -924,28 +940,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="F2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
       <x:c r="H2" s="24" t="str">
-        <x:v>来自 FissionModeratorRecipes 与 NCConfig 的 fission_moderator_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_moderator_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionModerator.add。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -997,7 +1013,7 @@
         <x:v>fission_moderator_flux_factor[0]; fission_moderator_efficiency[0]</x:v>
       </x:c>
       <x:c r="H4" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:616; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:18; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:64</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:374; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:381; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:18; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:64</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1023,7 +1039,7 @@
         <x:v>fission_moderator_flux_factor[1]; fission_moderator_efficiency[1]</x:v>
       </x:c>
       <x:c r="H5" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:616; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:19; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:65</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:374; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:381; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:19; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:65</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1049,7 +1065,85 @@
         <x:v>fission_moderator_flux_factor[2]; fission_moderator_efficiency[2]</x:v>
       </x:c>
       <x:c r="H6" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:616; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:20</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:374; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:381; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionModeratorRecipes.java:20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="26" t="str">
+        <x:v>减速剂</x:v>
+      </x:c>
+      <x:c r="B7" s="26" t="str">
+        <x:v>contenttweaker:water_mod</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="str">
+        <x:v>轻水减速剂</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>Light Water Moderator</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="str">
+        <x:v>CraftTweaker: FissionModerator.add(&lt;contenttweaker:water_mod&gt;, 29, 0.95)</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs:26; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs:37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="26" t="str">
+        <x:v>减速剂</x:v>
+      </x:c>
+      <x:c r="B8" s="26" t="str">
+        <x:v>contenttweaker:pu_schmeared_be_mod</x:v>
+      </x:c>
+      <x:c r="C8" s="26" t="str">
+        <x:v>钚-238 涂层铍减速剂</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>Plutonium-238 Schmeared Beryllium Moderator</x:v>
+      </x:c>
+      <x:c r="E8" s="26" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="G8" s="26" t="str">
+        <x:v>CraftTweaker: FissionModerator.add(&lt;contenttweaker:pu_schmeared_be_mod&gt;, 49, 0.98)</x:v>
+      </x:c>
+      <x:c r="H8" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs:36; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs:40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="26" t="str">
+        <x:v>减速剂</x:v>
+      </x:c>
+      <x:c r="B9" s="26" t="str">
+        <x:v>contenttweaker:hydrocarbon_mod</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>烃基减速剂</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>Hydrocarbon Moderator</x:v>
+      </x:c>
+      <x:c r="E9" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="G9" s="26" t="str">
+        <x:v>CraftTweaker: FissionModerator.add(&lt;contenttweaker:hydrocarbon_mod&gt;, 3, 1.02)</x:v>
+      </x:c>
+      <x:c r="H9" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs:46; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs:56</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1059,7 +1153,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a38380b4d1545fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80f64b58e3f3449c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1110,31 +1204,31 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="F2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="H2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
       <x:c r="I2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronReflectorType、FissionReflectorRecipes 与 NCConfig 的 fission_reflector_* 数组。</x:v>
+        <x:v>基础项来自 GreedyCraft nuclearcraft.cfg 的 fission_reflector_* 数组；MoarReactorComponents 附加项来自 CraftTweaker FissionReflector.add。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1192,7 +1286,7 @@
         <x:v>fission_reflector_efficiency[0]; fission_reflector_reflectivity[0]</x:v>
       </x:c>
       <x:c r="I4" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:618; NuclearCraft/src/main/java/nc/config/NCConfig.java:619; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:356; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionReflectorRecipes.java:21</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:388; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:394; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:356; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionReflectorRecipes.java:21</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1221,7 +1315,61 @@
         <x:v>fission_reflector_efficiency[1]; fission_reflector_reflectivity[1]</x:v>
       </x:c>
       <x:c r="I5" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:618; NuclearCraft/src/main/java/nc/config/NCConfig.java:619; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:357; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionReflectorRecipes.java:21</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:388; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:394; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:357; NuclearCraft/src/main/java/nc/recipe/multiblock/FissionReflectorRecipes.java:21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="26" t="str">
+        <x:v>反射器</x:v>
+      </x:c>
+      <x:c r="B6" s="26" t="str"/>
+      <x:c r="C6" s="26" t="str">
+        <x:v>contenttweaker:cf_neutron_multiplier</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>锎中子反射器（增殖器）</x:v>
+      </x:c>
+      <x:c r="E6" s="26" t="str">
+        <x:v>Neutron Reflector-Multiplier</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="G6" s="26" t="n">
+        <x:v>1.65</x:v>
+      </x:c>
+      <x:c r="H6" s="26" t="str">
+        <x:v>CraftTweaker: FissionReflector.add(&lt;contenttweaker:cf_neutron_multiplier&gt;, 0.65, 1.65)</x:v>
+      </x:c>
+      <x:c r="I6" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs:77; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs:61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="26" t="str">
+        <x:v>反射器</x:v>
+      </x:c>
+      <x:c r="B7" s="26" t="str"/>
+      <x:c r="C7" s="26" t="str">
+        <x:v>contenttweaker:gold_reflector</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>金-碳中子反射器</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="str">
+        <x:v>Gold-Carbon Neutron Reflector</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="str">
+        <x:v>CraftTweaker: FissionReflector.add(&lt;contenttweaker:gold_reflector&gt;, 0.6, 0.8)</x:v>
+      </x:c>
+      <x:c r="I7" s="26" t="str">
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/generation.zs:87; ../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/scripts/nc_script_addons/MoarReactorComponents/recipes_mrc.zs:66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1231,7 +1379,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3012196511434c40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45df67d918094eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1278,28 +1426,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="F2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
       <x:c r="H2" s="24" t="str">
-        <x:v>来自 MetaEnums.NeutronSourceType、NCBlocks 注册与 NCConfig 的 fission_source_efficiency 数组。</x:v>
+        <x:v>数值来自 GreedyCraft nuclearcraft.cfg 的 fission_source_efficiency 数组；类型与注册来自 MetaEnums.NeutronSourceType 和 NCBlocks。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1351,7 +1499,7 @@
         <x:v>fission_source_efficiency[0]</x:v>
       </x:c>
       <x:c r="H4" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:606; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:397; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:174; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:397; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1377,7 +1525,7 @@
         <x:v>fission_source_efficiency[1]</x:v>
       </x:c>
       <x:c r="H5" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:606; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:398; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:174; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:398; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1403,7 +1551,7 @@
         <x:v>fission_source_efficiency[2]</x:v>
       </x:c>
       <x:c r="H6" s="26" t="str">
-        <x:v>NuclearCraft/src/main/java/nc/config/NCConfig.java:606; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:244; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
+        <x:v>../GreedyCraft2/.minecraft/versions/GreedyCraft2 2.8.4 test11/config/nuclearcraft.cfg:174; NuclearCraft/src/main/java/nc/enumm/MetaEnums.java:399; NuclearCraft/src/main/java/nc/init/NCBlocks.java:392</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1413,7 +1561,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428697fdbd304845"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf24be3d69bce4e8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1601,7 +1749,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d9f0299c2f4fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re91bccd91ae841f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1821,7 +1969,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R467b4b372b074fd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb64c3f4eeda84329"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5929,7 +6077,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e2db98082f47ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3037a275eb964ef2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17553,7 +17701,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f76814083fd4419"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ff1cad4ea7e49a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17891,7 +18039,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R162c9333821f4293"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3b1674075a9446f"/>
   </x:tableParts>
 </x:worksheet>
 </file>